--- a/data/trans_dic/ProbViv_estruc-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre)</t>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 8,53</t>
+          <t>0,79; 9,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 13,6</t>
+          <t>2,3; 13,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 8,92</t>
+          <t>2,18; 8,74</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,61; 21,22</t>
+          <t>5,07; 21,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,26; 14,91</t>
+          <t>5,2; 15,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 15,69</t>
+          <t>6,84; 15,29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,7; 21,96</t>
+          <t>8,07; 22,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 15,97</t>
+          <t>4,86; 16,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 16,17</t>
+          <t>7,06; 16,25</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 11,22</t>
+          <t>1,52; 10,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 15,37</t>
+          <t>1,89; 15,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 10,31</t>
+          <t>2,68; 11,23</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,79</t>
+          <t>0,0; 6,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 12,96</t>
+          <t>1,39; 14,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,06</t>
+          <t>0,78; 7,7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,75; 15,24</t>
+          <t>2,77; 16,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,91; 13,16</t>
+          <t>2,95; 13,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,7; 11,67</t>
+          <t>4,02; 11,67</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,23; 17,64</t>
+          <t>5,89; 17,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,43; 15,78</t>
+          <t>6,45; 15,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,1; 13,79</t>
+          <t>7,14; 13,95</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,13; 20,37</t>
+          <t>10,08; 20,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,96; 21,39</t>
+          <t>10,47; 21,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,11; 19,36</t>
+          <t>11,93; 19,16</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,77; 12,4</t>
+          <t>7,72; 12,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,69; 11,81</t>
+          <t>7,82; 11,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,24; 11,28</t>
+          <t>8,24; 11,26</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2244</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4968</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7212</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>578; 6930</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1823; 10760</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3321; 13345</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>15746</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11403</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>27149</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6468; 26984</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6631; 19135</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>17455; 39021</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8110</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6270</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14381</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4701; 13122</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3265; 10894</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8853; 20377</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3258</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4547</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7804</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1054; 7348</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1475; 11978</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3947; 16543</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2420</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2267</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>566; 5784</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>586; 5796</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3409</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3840</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7249</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1277; 7409</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1656; 7578</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>4112; 11940</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>12322</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>15831</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>28153</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>7339; 21358</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>9999; 24292</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>19963; 38999</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>19313</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>24453</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>43766</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>13272; 27215</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>16416; 32955</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>34419; 55255</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>64805</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>73329</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>138135</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>51383; 83388</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>59503; 88982</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>117506; 160601</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/ProbViv_estruc-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Provincia-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 9,46</t>
+          <t>0,75; 8,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 13,56</t>
+          <t>2,43; 12,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,74</t>
+          <t>2,09; 8,88</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 21,14</t>
+          <t>5,53; 20,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 15,0</t>
+          <t>5,15; 14,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,84; 15,29</t>
+          <t>6,66; 15,15</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,07; 22,52</t>
+          <t>7,41; 21,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,86; 16,22</t>
+          <t>4,58; 15,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,06; 16,25</t>
+          <t>7,55; 16,25</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 10,63</t>
+          <t>1,66; 11,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 15,33</t>
+          <t>1,76; 14,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 11,23</t>
+          <t>2,54; 10,44</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,57</t>
+          <t>0,0; 6,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 14,2</t>
+          <t>1,38; 13,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,7</t>
+          <t>0,99; 7,74</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 16,05</t>
+          <t>3,32; 15,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,95; 13,49</t>
+          <t>2,77; 13,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,02; 11,67</t>
+          <t>3,85; 11,95</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,89; 17,15</t>
+          <t>6,11; 16,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,45; 15,67</t>
+          <t>6,16; 15,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,14; 13,95</t>
+          <t>7,17; 14,23</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,08; 20,68</t>
+          <t>10,0; 20,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,47; 21,02</t>
+          <t>10,76; 21,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,93; 19,16</t>
+          <t>11,77; 18,62</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,72; 12,54</t>
+          <t>7,62; 12,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,82; 11,69</t>
+          <t>7,63; 11,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,24; 11,26</t>
+          <t>8,22; 11,2</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>578; 6930</t>
+          <t>548; 5883</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1823; 10760</t>
+          <t>1930; 10126</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3321; 13345</t>
+          <t>3188; 13557</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6468; 26984</t>
+          <t>7057; 26765</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6631; 19135</t>
+          <t>6577; 18231</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17455; 39021</t>
+          <t>17011; 38681</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4701; 13122</t>
+          <t>4319; 12388</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3265; 10894</t>
+          <t>3077; 10536</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8853; 20377</t>
+          <t>9474; 20378</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1054; 7348</t>
+          <t>1148; 7684</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1475; 11978</t>
+          <t>1374; 11461</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3947; 16543</t>
+          <t>3736; 15371</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2267</t>
+          <t>0; 2080</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>566; 5784</t>
+          <t>564; 5462</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>586; 5796</t>
+          <t>747; 5822</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1277; 7409</t>
+          <t>1533; 7357</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1656; 7578</t>
+          <t>1556; 7553</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4112; 11940</t>
+          <t>3941; 12231</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7339; 21358</t>
+          <t>7605; 20840</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9999; 24292</t>
+          <t>9554; 23463</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19963; 38999</t>
+          <t>20038; 39782</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>13272; 27215</t>
+          <t>13156; 26420</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>16416; 32955</t>
+          <t>16874; 33865</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>34419; 55255</t>
+          <t>33953; 53697</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>51383; 83388</t>
+          <t>50689; 81698</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>59503; 88982</t>
+          <t>58030; 90503</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>117506; 160601</t>
+          <t>117272; 159766</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProbViv_estruc-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 8,03</t>
+          <t>2,16; 12,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 12,76</t>
+          <t>0,84; 8,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,88</t>
+          <t>2,19; 9,01</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 20,97</t>
+          <t>5,0; 14,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,15; 14,29</t>
+          <t>8,34; 20,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 15,15</t>
+          <t>7,85; 15,13</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,41; 21,26</t>
+          <t>4,67; 15,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 15,69</t>
+          <t>8,17; 22,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,55; 16,25</t>
+          <t>7,46; 16,5</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 11,11</t>
+          <t>1,59; 15,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 14,67</t>
+          <t>1,56; 11,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 10,44</t>
+          <t>2,25; 10,07</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,03</t>
+          <t>1,22; 13,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 13,41</t>
+          <t>0,0; 7,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 7,74</t>
+          <t>0,79; 7,87</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,32; 15,94</t>
+          <t>2,75; 13,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 13,44</t>
+          <t>2,82; 15,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,85; 11,95</t>
+          <t>3,8; 12,09</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,11; 16,74</t>
+          <t>6,59; 16,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,16; 15,13</t>
+          <t>5,2; 13,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,17; 14,23</t>
+          <t>6,75; 13,02</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,0; 20,07</t>
+          <t>11,05; 21,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,76; 21,6</t>
+          <t>9,74; 20,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,77; 18,62</t>
+          <t>11,89; 19,42</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,62; 12,28</t>
+          <t>7,84; 11,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,63; 11,89</t>
+          <t>7,92; 12,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,22; 11,2</t>
+          <t>8,45; 11,21</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>5647</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>548; 5883</t>
+          <t>1388; 7994</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1930; 10126</t>
+          <t>472; 5024</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3188; 13557</t>
+          <t>2636; 10872</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>15746</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11403</t>
+          <t>13553</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27149</t>
+          <t>23477</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7057; 26765</t>
+          <t>5791; 16938</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6577; 18231</t>
+          <t>8452; 20797</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17011; 38681</t>
+          <t>17054; 32869</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>13633</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4319; 12388</t>
+          <t>2773; 9487</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3077; 10536</t>
+          <t>4623; 12859</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9474; 20378</t>
+          <t>8648; 19126</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>7036</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1148; 7684</t>
+          <t>1145; 11127</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1374; 11461</t>
+          <t>1086; 7920</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3736; 15371</t>
+          <t>3187; 14298</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>541</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>2467</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2080</t>
+          <t>483; 5308</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>564; 5462</t>
+          <t>0; 2770</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>747; 5822</t>
+          <t>590; 5915</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>6808</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1533; 7357</t>
+          <t>1347; 6441</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1556; 7553</t>
+          <t>1289; 7209</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3941; 12231</t>
+          <t>3595; 11454</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>12322</t>
+          <t>14725</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>15831</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28153</t>
+          <t>25237</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>7605; 20840</t>
+          <t>9258; 22798</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9554; 23463</t>
+          <t>6374; 16527</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20038; 39782</t>
+          <t>17748; 34226</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>19313</t>
+          <t>25218</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>24453</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43766</t>
+          <t>45235</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>13156; 26420</t>
+          <t>17619; 34576</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>16874; 33865</t>
+          <t>13679; 28910</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>33953; 53697</t>
+          <t>35654; 58254</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>94</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>64805</t>
+          <t>68184</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>73329</t>
+          <t>61356</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>138135</t>
+          <t>129540</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>50689; 81698</t>
+          <t>54905; 83074</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>58030; 90503</t>
+          <t>49795; 75604</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>117272; 159766</t>
+          <t>112229; 148939</t>
         </is>
       </c>
     </row>
